--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>57.75</v>
+        <v>167</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
@@ -920,12 +920,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>167</v>
+        <v>57.75</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>50</v>
+        <v>20.97</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1296,12 +1296,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20.97</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Longreach Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1544,15 +1544,13 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>17</v>
+        <v>92.5</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1593,12 +1591,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Longreach Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1607,13 +1605,15 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>92.5</v>
+        <v>17</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="H18" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1780,7 +1780,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9648</v>
@@ -2124,7 +2124,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0.9648</v>
@@ -2240,12 +2240,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>GERMCRK</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek Power Station</t>
+          <t>German Creek Power Station</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>44.976</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1.0373</v>
@@ -2307,12 +2307,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek 2</t>
+          <t>Oaky Creek Power Station</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1.0373</v>
@@ -2374,12 +2374,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GERMCRK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>German Creek Power Station</t>
+          <t>Oaky Creek 2</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>44.976</v>
+        <v>15</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1.0373</v>
@@ -2441,7 +2441,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2449,11 +2449,7 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="4" t="n">
         <v>30</v>
       </c>
@@ -2496,7 +2492,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2504,7 +2500,11 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n">
         <v>30</v>
       </c>
@@ -2614,7 +2614,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr"/>
@@ -3113,32 +3113,24 @@
       <c r="P42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q42" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S42" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U42" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V42" s="5" t="n">
-        <v>-0.0043</v>
-      </c>
-      <c r="W42" s="6" t="n">
-        <v>-0.46</v>
-      </c>
+      <c r="V42" s="5" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3148,11 +3140,11 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr"/>
@@ -3168,19 +3160,27 @@
       <c r="P43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="R43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="n">
+        <v>0.9247</v>
+      </c>
       <c r="T43" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U43" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V43" s="5" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
+      <c r="V43" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3257,17 +3257,13 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Stanwell Battery Energy Storage System</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>317</v>
-      </c>
+          <t>STABESS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
@@ -3508,7 +3504,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3575,7 +3571,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3642,7 +3638,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE1</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3709,7 +3705,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3776,7 +3772,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3790,7 +3786,7 @@
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>345.5</v>
+        <v>103.5</v>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="inlineStr"/>
@@ -3825,7 +3821,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3839,7 +3835,7 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>103.5</v>
+        <v>345.5</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
@@ -4210,7 +4206,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4277,7 +4273,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4779,7 +4775,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4789,11 +4785,11 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="5" t="inlineStr"/>
@@ -4836,7 +4832,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4846,11 +4842,11 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="5" t="inlineStr"/>
@@ -4981,7 +4977,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5048,7 +5044,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA3</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5062,7 +5058,7 @@
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>1.069</v>
@@ -5115,7 +5111,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5129,7 +5125,7 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>1.069</v>
@@ -5182,7 +5178,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA3</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5430,12 +5426,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5444,7 +5440,7 @@
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>272.48</v>
+        <v>269.8</v>
       </c>
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="5" t="inlineStr"/>
@@ -5455,12 +5451,8 @@
       <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="5" t="inlineStr"/>
       <c r="M81" s="5" t="inlineStr"/>
-      <c r="N81" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="O81" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
       <c r="P81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5489,12 +5481,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5503,7 +5495,7 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>269.8</v>
+        <v>272.48</v>
       </c>
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr"/>
@@ -5514,8 +5506,12 @@
       <c r="K82" s="5" t="inlineStr"/>
       <c r="L82" s="5" t="inlineStr"/>
       <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr"/>
-      <c r="O82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="P82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5772,12 +5768,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Darling Downs Power Station</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5786,7 +5782,7 @@
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>173</v>
+        <v>644</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0.9567</v>
@@ -5839,7 +5835,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR5</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -5906,7 +5902,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR3</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -6040,7 +6036,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR3</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6107,7 +6103,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR5</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -6174,12 +6170,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DDPS1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Darling Downs Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6188,7 +6184,7 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>644</v>
+        <v>173</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0.9567</v>
@@ -6416,7 +6412,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -6483,7 +6479,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6550,7 +6546,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6617,7 +6613,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -6873,7 +6869,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1</t>
+          <t>OAKEY2</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6940,7 +6936,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2</t>
+          <t>OAKEY1</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7074,7 +7070,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -7141,7 +7137,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7208,7 +7204,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7275,7 +7271,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7458,53 +7454,41 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
+          <t>Edenvale Solar Park</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>21.287</v>
+        <v>180</v>
       </c>
       <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="5" t="n">
-        <v>1.0727</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="5" t="inlineStr"/>
+      <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="O113" s="5" t="inlineStr"/>
       <c r="P113" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="Q113" s="5" t="inlineStr"/>
       <c r="R113" s="5" t="n">
@@ -7512,10 +7496,10 @@
       </c>
       <c r="S113" s="5" t="inlineStr"/>
       <c r="T113" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0026</v>
       </c>
       <c r="U113" s="6" t="n">
-        <v>-1.8</v>
+        <v>-0.26</v>
       </c>
       <c r="V113" s="5" t="inlineStr"/>
       <c r="W113" s="6" t="inlineStr"/>
@@ -7523,41 +7507,51 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Edenvale Solar Park</t>
+          <t>Grosvenor 2</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>180</v>
+        <v>15.205</v>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="5" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="5" t="inlineStr"/>
-      <c r="K114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="L114" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="O114" s="5" t="inlineStr"/>
       <c r="P114" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="Q114" s="5" t="inlineStr"/>
       <c r="R114" s="5" t="n">
@@ -7565,10 +7559,10 @@
       </c>
       <c r="S114" s="5" t="inlineStr"/>
       <c r="T114" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.018</v>
       </c>
       <c r="U114" s="6" t="n">
-        <v>-0.26</v>
+        <v>-1.8</v>
       </c>
       <c r="V114" s="5" t="inlineStr"/>
       <c r="W114" s="6" t="inlineStr"/>
@@ -7576,12 +7570,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 2</t>
+          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -7590,10 +7584,12 @@
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>15.205</v>
+        <v>21.287</v>
       </c>
       <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="inlineStr"/>
+      <c r="F115" s="5" t="n">
+        <v>1.0727</v>
+      </c>
       <c r="G115" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -7774,17 +7770,13 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Woolooga BESS</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>280</v>
-      </c>
+          <t>WOOLOOGA</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="3" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
@@ -7926,22 +7918,18 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Wandoan Solar Farm</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>159</v>
-      </c>
+          <t>Wandoan Solar Farm 1</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="3" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
@@ -7949,15 +7937,9 @@
       <c r="I121" s="5" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="5" t="inlineStr"/>
-      <c r="L121" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr"/>
       <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -7979,12 +7961,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Wandoan Solar Farm</t>
+          <t>Wandoan Solar Farm 1</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -7993,7 +7975,7 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr"/>
@@ -8002,9 +7984,15 @@
       <c r="I122" s="5" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="5" t="inlineStr"/>
-      <c r="L122" s="5" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="O122" s="5" t="inlineStr"/>
       <c r="P122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -8093,12 +8081,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1SF</t>
+          <t>OAKEY2SF</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Oakey 1 Solar Farm</t>
+          <t>Oakey 2 Solar Farm</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8107,14 +8095,12 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="5" t="inlineStr"/>
       <c r="G124" s="5" t="inlineStr"/>
-      <c r="H124" s="5" t="n">
-        <v>0.9826</v>
-      </c>
+      <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -8154,12 +8140,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2SF</t>
+          <t>OAKEY1SF</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Oakey 2 Solar Farm</t>
+          <t>Oakey 1 Solar Farm</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -8168,12 +8154,14 @@
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr"/>
-      <c r="H125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="n">
+        <v>0.9826</v>
+      </c>
       <c r="I125" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -8213,47 +8201,41 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Yarranlea Solar Farm</t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="n">
-        <v>0.9872</v>
-      </c>
-      <c r="J126" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr"/>
       <c r="L126" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="O126" s="5" t="inlineStr"/>
       <c r="P126" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="Q126" s="5" t="inlineStr"/>
       <c r="R126" s="5" t="n">
@@ -8261,10 +8243,10 @@
       </c>
       <c r="S126" s="5" t="inlineStr"/>
       <c r="T126" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="U126" s="6" t="n">
-        <v>-0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V126" s="5" t="inlineStr"/>
       <c r="W126" s="6" t="inlineStr"/>
@@ -8272,12 +8254,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Maryrorough Solar Farm</t>
+          <t>Warwick Solar Farm 2</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -8286,15 +8268,13 @@
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="I127" s="5" t="inlineStr"/>
       <c r="J127" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8388,41 +8368,47 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t>Maryrorough Solar Farm</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="5" t="inlineStr"/>
       <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="5" t="inlineStr"/>
-      <c r="K129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L129" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="O129" s="5" t="inlineStr"/>
       <c r="P129" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="Q129" s="5" t="inlineStr"/>
       <c r="R129" s="5" t="n">
@@ -8430,10 +8416,10 @@
       </c>
       <c r="S129" s="5" t="inlineStr"/>
       <c r="T129" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="U129" s="6" t="n">
-        <v>0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="V129" s="5" t="inlineStr"/>
       <c r="W129" s="6" t="inlineStr"/>
@@ -8441,12 +8427,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Warwick Solar Farm 2</t>
+          <t>Yarranlea Solar Farm</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8455,13 +8441,15 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="J130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8933,62 +8921,70 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>DG_QLD1</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Supernode BESS</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr"/>
       <c r="D138" s="4" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="5" t="inlineStr"/>
-      <c r="L138" s="5" t="inlineStr"/>
-      <c r="M138" s="5" t="inlineStr"/>
-      <c r="N138" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O138" s="5" t="inlineStr"/>
       <c r="P138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q138" s="5" t="inlineStr"/>
       <c r="R138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S138" s="5" t="inlineStr"/>
       <c r="T138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U138" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="V138" s="5" t="inlineStr"/>
+      <c r="W138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9043,65 +9039,57 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
+          <t>SNB01</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>QLD1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr"/>
+          <t>Supernode BESS</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D140" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>337.4</v>
+      </c>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
+      <c r="M140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="5" t="inlineStr"/>
       <c r="P140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" s="5" t="inlineStr"/>
+      <c r="Q140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="R140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S140" s="5" t="inlineStr"/>
+      <c r="S140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="T140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U140" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="5" t="inlineStr"/>
-      <c r="W140" s="6" t="inlineStr"/>
+      <c r="V140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -9436,12 +9424,12 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>BPLANDF1</t>
+          <t>STAPYLTON1</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Browns Plains Landfill Gas PS</t>
+          <t>Stapylton Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -9450,14 +9438,10 @@
         </is>
       </c>
       <c r="D147" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E147" s="5" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>1.008</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E147" s="5" t="inlineStr"/>
+      <c r="F147" s="5" t="inlineStr"/>
       <c r="G147" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -9503,12 +9487,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>BPLANDF1</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Rocky Point Cogeneration Plant</t>
+          <t>Browns Plains Landfill Gas PS</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -9517,7 +9501,7 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E148" s="5" t="n">
         <v>1.0078</v>
@@ -9570,12 +9554,12 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
+          <t>RPCG</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Stapylton Renewable Energy Facility</t>
+          <t>Rocky Point Cogeneration Plant</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -9584,10 +9568,14 @@
         </is>
       </c>
       <c r="D149" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E149" s="5" t="inlineStr"/>
-      <c r="F149" s="5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>1.008</v>
+      </c>
       <c r="G149" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -10038,12 +10026,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Whitwood Road Renewable Energy Facility</t>
+          <t>Roghan Road LFG Power Plant</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -10052,22 +10040,22 @@
         </is>
       </c>
       <c r="D157" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="J157" s="5" t="inlineStr"/>
       <c r="K157" s="5" t="inlineStr"/>
@@ -10087,12 +10075,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Rochedale Renewable Energy Facility</t>
+          <t>Whitwood Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -10101,22 +10089,22 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="J158" s="5" t="inlineStr"/>
       <c r="K158" s="5" t="inlineStr"/>
@@ -10136,12 +10124,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Roghan Road LFG Power Plant</t>
+          <t>Rochedale Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10150,22 +10138,22 @@
         </is>
       </c>
       <c r="D159" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="J159" s="5" t="inlineStr"/>
       <c r="K159" s="5" t="inlineStr"/>
@@ -10346,22 +10334,18 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>WDBESSG1</t>
+          <t>BBATTERY</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>272</v>
-      </c>
+          <t>Bouldercombe Battery Project</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D163" s="3" t="inlineStr"/>
       <c r="E163" s="5" t="inlineStr"/>
       <c r="F163" s="5" t="inlineStr"/>
       <c r="G163" s="5" t="inlineStr"/>
@@ -10371,10 +10355,10 @@
       <c r="K163" s="5" t="inlineStr"/>
       <c r="L163" s="5" t="inlineStr"/>
       <c r="M163" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9198</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>0.9556</v>
+        <v>0.9166</v>
       </c>
       <c r="O163" s="5" t="inlineStr"/>
       <c r="P163" s="5" t="inlineStr"/>
@@ -10389,12 +10373,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>WANDBG1</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Wandoan BESS</t>
+          <t>Chinchilla BESS</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -10403,7 +10387,7 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E164" s="5" t="inlineStr"/>
       <c r="F164" s="5" t="inlineStr"/>
@@ -10411,17 +10395,13 @@
       <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="inlineStr"/>
       <c r="J164" s="5" t="inlineStr"/>
-      <c r="K164" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v>0.9767</v>
-      </c>
+      <c r="K164" s="5" t="inlineStr"/>
+      <c r="L164" s="5" t="inlineStr"/>
       <c r="M164" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9588</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9611</v>
       </c>
       <c r="O164" s="5" t="inlineStr"/>
       <c r="P164" s="5" t="inlineStr"/>
@@ -10436,12 +10416,12 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>WDBESSG1</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Chinchilla BESS</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -10450,7 +10430,7 @@
         </is>
       </c>
       <c r="D165" s="4" t="n">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="E165" s="5" t="inlineStr"/>
       <c r="F165" s="5" t="inlineStr"/>
@@ -10461,10 +10441,10 @@
       <c r="K165" s="5" t="inlineStr"/>
       <c r="L165" s="5" t="inlineStr"/>
       <c r="M165" s="5" t="n">
-        <v>0.9588</v>
+        <v>0.9586</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9556</v>
       </c>
       <c r="O165" s="5" t="inlineStr"/>
       <c r="P165" s="5" t="inlineStr"/>
@@ -10479,31 +10459,39 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>WANDBG1</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Bouldercombe Battery Project</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D166" s="3" t="inlineStr"/>
+          <t>Wandoan BESS</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>123</v>
+      </c>
       <c r="E166" s="5" t="inlineStr"/>
       <c r="F166" s="5" t="inlineStr"/>
       <c r="G166" s="5" t="inlineStr"/>
       <c r="H166" s="5" t="inlineStr"/>
       <c r="I166" s="5" t="inlineStr"/>
       <c r="J166" s="5" t="inlineStr"/>
-      <c r="K166" s="5" t="inlineStr"/>
-      <c r="L166" s="5" t="inlineStr"/>
+      <c r="K166" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>0.9767</v>
+      </c>
       <c r="M166" s="5" t="n">
-        <v>0.9198</v>
+        <v>0.9751</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>0.9166</v>
+        <v>0.9823</v>
       </c>
       <c r="O166" s="5" t="inlineStr"/>
       <c r="P166" s="5" t="inlineStr"/>
@@ -10798,7 +10786,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -10838,7 +10826,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -11046,7 +11034,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
@@ -11088,7 +11076,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
@@ -11238,16 +11226,14 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11280,14 +11266,16 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11404,7 +11392,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -11430,7 +11418,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
@@ -11576,7 +11564,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -11622,7 +11610,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -11696,7 +11684,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>GERMCRK</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -11742,7 +11730,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -11788,7 +11776,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GERMCRK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -11834,7 +11822,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -11872,7 +11860,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -11956,7 +11944,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -12002,7 +11990,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -12048,7 +12036,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -12278,7 +12266,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
@@ -12295,20 +12283,16 @@
       <c r="M42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N42" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P42" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="P42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr"/>
@@ -12325,11 +12309,15 @@
       <c r="M43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="O43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="n">
+        <v>0.9247</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12548,7 +12536,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -12594,7 +12582,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE1</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -12640,7 +12628,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE1</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -12686,7 +12674,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -12732,7 +12720,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
@@ -12760,7 +12748,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
@@ -12994,7 +12982,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -13040,7 +13028,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -13374,7 +13362,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr"/>
@@ -13410,7 +13398,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
@@ -13496,7 +13484,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -13542,7 +13530,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA3</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -13588,7 +13576,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -13634,7 +13622,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA3</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -13798,7 +13786,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
@@ -13810,12 +13798,8 @@
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr"/>
-      <c r="K81" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr"/>
       <c r="M81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -13832,7 +13816,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
@@ -13844,8 +13828,12 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="5" t="inlineStr"/>
-      <c r="L82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="M82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -13998,7 +13986,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -14044,7 +14032,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR5</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
@@ -14090,7 +14078,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR3</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -14182,7 +14170,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR3</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -14228,7 +14216,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR5</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -14274,7 +14262,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DDPS1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -14428,7 +14416,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -14474,7 +14462,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -14520,7 +14508,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -14566,7 +14554,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -14738,7 +14726,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1</t>
+          <t>OAKEY2</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -14784,7 +14772,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2</t>
+          <t>OAKEY1</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -14876,7 +14864,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -14922,7 +14910,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -14968,7 +14956,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -15014,7 +15002,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -15134,40 +15122,28 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr"/>
-      <c r="C113" s="5" t="n">
-        <v>1.0727</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="C113" s="5" t="inlineStr"/>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="N113" s="5" t="inlineStr"/>
       <c r="O113" s="5" t="n">
@@ -15178,28 +15154,38 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr"/>
       <c r="C114" s="5" t="inlineStr"/>
-      <c r="D114" s="5" t="inlineStr"/>
-      <c r="E114" s="5" t="inlineStr"/>
-      <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="5" t="inlineStr"/>
+      <c r="D114" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="I114" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="L114" s="5" t="inlineStr"/>
       <c r="M114" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="N114" s="5" t="inlineStr"/>
       <c r="O114" s="5" t="n">
@@ -15210,11 +15196,13 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr"/>
-      <c r="C115" s="5" t="inlineStr"/>
+      <c r="C115" s="5" t="n">
+        <v>1.0727</v>
+      </c>
       <c r="D115" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -15430,7 +15418,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr"/>
@@ -15440,15 +15428,9 @@
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="J121" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr"/>
+      <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15462,7 +15444,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr"/>
@@ -15472,9 +15454,15 @@
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="5" t="inlineStr"/>
-      <c r="K122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15534,15 +15522,13 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1SF</t>
+          <t>OAKEY2SF</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr"/>
       <c r="C124" s="5" t="inlineStr"/>
       <c r="D124" s="5" t="inlineStr"/>
-      <c r="E124" s="5" t="n">
-        <v>0.9826</v>
-      </c>
+      <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -15574,13 +15560,15 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2SF</t>
+          <t>OAKEY1SF</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr"/>
       <c r="C125" s="5" t="inlineStr"/>
       <c r="D125" s="5" t="inlineStr"/>
-      <c r="E125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>0.9826</v>
+      </c>
       <c r="F125" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -15612,34 +15600,28 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr"/>
       <c r="C126" s="5" t="inlineStr"/>
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="5" t="n">
-        <v>0.9872</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="5" t="n">
@@ -15650,16 +15632,14 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr"/>
       <c r="C127" s="5" t="inlineStr"/>
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr"/>
-      <c r="F127" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -15724,28 +15704,34 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr"/>
       <c r="C129" s="5" t="inlineStr"/>
       <c r="D129" s="5" t="inlineStr"/>
       <c r="E129" s="5" t="inlineStr"/>
-      <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr"/>
+      <c r="F129" s="5" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="I129" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="L129" s="5" t="inlineStr"/>
       <c r="M129" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="N129" s="5" t="inlineStr"/>
       <c r="O129" s="5" t="n">
@@ -15756,14 +15742,16 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr"/>
       <c r="C130" s="5" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
+      <c r="F130" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="G130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -16076,37 +16064,53 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr"/>
-      <c r="C138" s="5" t="inlineStr"/>
-      <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>DG_QLD1</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N138" s="5" t="inlineStr"/>
       <c r="O138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr"/>
@@ -16136,48 +16140,32 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>SNB01</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr"/>
+      <c r="C140" s="5" t="inlineStr"/>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr"/>
       <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P140" s="5" t="inlineStr"/>
+      <c r="P140" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -16386,15 +16374,11 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>BPLANDF1</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="C147" s="5" t="n">
-        <v>1.008</v>
-      </c>
+          <t>STAPYLTON1</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr"/>
+      <c r="C147" s="5" t="inlineStr"/>
       <c r="D147" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -16432,7 +16416,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>BPLANDF1</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
@@ -16478,11 +16462,15 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr"/>
-      <c r="C149" s="5" t="inlineStr"/>
+          <t>RPCG</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>1.008</v>
+      </c>
       <c r="D149" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -16790,23 +16778,23 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="5" t="inlineStr"/>
@@ -16822,23 +16810,23 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="5" t="inlineStr"/>
@@ -16854,23 +16842,23 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
       <c r="H159" s="5" t="inlineStr"/>
@@ -16996,7 +16984,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>WDBESSG1</t>
+          <t>BBATTERY</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr"/>
@@ -17008,10 +16996,10 @@
       <c r="H163" s="5" t="inlineStr"/>
       <c r="I163" s="5" t="inlineStr"/>
       <c r="J163" s="5" t="n">
-        <v>0.9586</v>
+        <v>0.9198</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>0.9556</v>
+        <v>0.9166</v>
       </c>
       <c r="L163" s="5" t="inlineStr"/>
       <c r="M163" s="5" t="inlineStr"/>
@@ -17022,7 +17010,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>WANDBG1</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr"/>
@@ -17031,17 +17019,13 @@
       <c r="E164" s="5" t="inlineStr"/>
       <c r="F164" s="5" t="inlineStr"/>
       <c r="G164" s="5" t="inlineStr"/>
-      <c r="H164" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="I164" s="5" t="n">
-        <v>0.9767</v>
-      </c>
+      <c r="H164" s="5" t="inlineStr"/>
+      <c r="I164" s="5" t="inlineStr"/>
       <c r="J164" s="5" t="n">
-        <v>0.9751</v>
+        <v>0.9588</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9611</v>
       </c>
       <c r="L164" s="5" t="inlineStr"/>
       <c r="M164" s="5" t="inlineStr"/>
@@ -17052,7 +17036,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>WDBESSG1</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr"/>
@@ -17064,10 +17048,10 @@
       <c r="H165" s="5" t="inlineStr"/>
       <c r="I165" s="5" t="inlineStr"/>
       <c r="J165" s="5" t="n">
-        <v>0.9588</v>
+        <v>0.9586</v>
       </c>
       <c r="K165" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9556</v>
       </c>
       <c r="L165" s="5" t="inlineStr"/>
       <c r="M165" s="5" t="inlineStr"/>
@@ -17078,7 +17062,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>WANDBG1</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr"/>
@@ -17087,13 +17071,17 @@
       <c r="E166" s="5" t="inlineStr"/>
       <c r="F166" s="5" t="inlineStr"/>
       <c r="G166" s="5" t="inlineStr"/>
-      <c r="H166" s="5" t="inlineStr"/>
-      <c r="I166" s="5" t="inlineStr"/>
+      <c r="H166" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>0.9767</v>
+      </c>
       <c r="J166" s="5" t="n">
-        <v>0.9198</v>
+        <v>0.9751</v>
       </c>
       <c r="K166" s="5" t="n">
-        <v>0.9166</v>
+        <v>0.9823</v>
       </c>
       <c r="L166" s="5" t="inlineStr"/>
       <c r="M166" s="5" t="inlineStr"/>
@@ -17409,7 +17397,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -17438,7 +17426,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -17554,12 +17542,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -17583,12 +17571,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -17699,12 +17687,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17728,12 +17716,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -17815,12 +17803,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17873,12 +17861,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -17975,7 +17963,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -18033,7 +18021,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -18154,13 +18142,11 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Woolooga BESS</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
+          <t>WOOLOOGA</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v/>
       </c>
       <c r="D33" s="5" t="n">
         <v>0.9824000000000001</v>
@@ -18294,7 +18280,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -18323,7 +18309,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -18381,12 +18367,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -18410,12 +18396,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -18526,12 +18512,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Darling Downs Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -3257,13 +3257,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>STABESS</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
+          <t>Stanwell Battery Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>317</v>
+      </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
@@ -7770,13 +7774,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>WOOLOOGA</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="3" t="inlineStr"/>
+          <t>Woolooga BESS</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>280</v>
+      </c>
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
@@ -7923,13 +7931,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Wandoan Solar Farm 1</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="3" t="inlineStr"/>
+          <t>Wandoan Solar Farm</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>310</v>
+      </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
@@ -7966,7 +7978,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Wandoan Solar Farm 1</t>
+          <t>Wandoan Solar Farm</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -18142,11 +18154,13 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>WOOLOOGA</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v/>
+          <t>Woolooga BESS</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>0.9824000000000001</v>

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W166"/>
+  <dimension ref="A1:W164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>167</v>
+        <v>57.75</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
@@ -920,12 +920,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>57.75</v>
+        <v>167</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>20.97</v>
+        <v>50</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1296,12 +1296,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>50</v>
+        <v>20.97</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1544,13 +1544,17 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>92.5</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>1.0107</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
       <c r="H17" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1654,12 +1658,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1668,17 +1672,13 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>20</v>
+        <v>92.5</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="n">
-        <v>1.0107</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.9715</v>
-      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1780,7 +1780,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9648</v>
@@ -2124,7 +2124,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0.9648</v>
@@ -2307,12 +2307,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek Power Station</t>
+          <t>Oaky Creek 2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1.0373</v>
@@ -2374,12 +2374,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek 2</t>
+          <t>Oaky Creek Power Station</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1.0373</v>
@@ -2441,7 +2441,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2449,7 +2449,11 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n">
         <v>30</v>
       </c>
@@ -2492,7 +2496,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2500,11 +2504,7 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="4" t="n">
         <v>30</v>
       </c>
@@ -2547,7 +2547,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr"/>
@@ -3113,24 +3113,32 @@
       <c r="P42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="R42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S42" s="5" t="inlineStr"/>
+      <c r="S42" s="5" t="n">
+        <v>0.9247</v>
+      </c>
       <c r="T42" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U42" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V42" s="5" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
+      <c r="V42" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="W42" s="6" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3140,11 +3148,11 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr"/>
@@ -3160,27 +3168,19 @@
       <c r="P43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q43" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S43" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U43" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V43" s="5" t="n">
-        <v>-0.0043</v>
-      </c>
-      <c r="W43" s="6" t="n">
-        <v>-0.46</v>
-      </c>
+      <c r="V43" s="5" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>GLADSTONE POWER STATION</t>
+          <t>Gladstone Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0.9855</v>
@@ -3441,12 +3441,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Gladstone Power Station</t>
+          <t>GLADSTONE POWER STATION</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.9855</v>
@@ -3508,7 +3508,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>103.5</v>
+        <v>345.5</v>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="inlineStr"/>
@@ -3825,7 +3825,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>345.5</v>
+        <v>103.5</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
@@ -3945,7 +3945,9 @@
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="n">
+        <v>0.9198</v>
+      </c>
       <c r="N56" s="5" t="n">
         <v>0.9166</v>
       </c>
@@ -4210,7 +4212,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4277,7 +4279,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4466,7 +4468,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4480,7 +4482,7 @@
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>1.0156</v>
@@ -4600,7 +4602,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4614,7 +4616,7 @@
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>1.0156</v>
@@ -4722,7 +4724,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4743,36 +4745,20 @@
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="inlineStr"/>
-      <c r="P69" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="P69" s="5" t="inlineStr"/>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S69" s="5" t="inlineStr"/>
-      <c r="T69" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="U69" s="6" t="n">
-        <v>-2.44</v>
-      </c>
+      <c r="T69" s="5" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr"/>
       <c r="V69" s="5" t="inlineStr"/>
       <c r="W69" s="6" t="inlineStr"/>
     </row>
@@ -4836,21 +4822,21 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park</t>
+          <t>Kennedy Energy Park Battery</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="5" t="inlineStr"/>
@@ -4893,41 +4879,57 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park Battery</t>
+          <t>Kennedy Energy Park</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="5" t="inlineStr"/>
-      <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr"/>
-      <c r="N72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="N72" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="5" t="inlineStr"/>
+      <c r="P72" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="Q72" s="5" t="inlineStr"/>
       <c r="R72" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S72" s="5" t="inlineStr"/>
-      <c r="T72" s="5" t="inlineStr"/>
-      <c r="U72" s="6" t="inlineStr"/>
+      <c r="T72" s="5" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="U72" s="6" t="n">
+        <v>-2.44</v>
+      </c>
       <c r="V72" s="5" t="inlineStr"/>
       <c r="W72" s="6" t="inlineStr"/>
     </row>
@@ -4981,7 +4983,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5048,7 +5050,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5062,7 +5064,7 @@
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>1.069</v>
@@ -5115,7 +5117,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5249,7 +5251,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5263,7 +5265,7 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>1.069</v>
@@ -5430,12 +5432,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5444,7 +5446,7 @@
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>269.8</v>
+        <v>272.48</v>
       </c>
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="5" t="inlineStr"/>
@@ -5454,9 +5456,15 @@
       <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="5" t="inlineStr"/>
-      <c r="M81" s="5" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr"/>
-      <c r="O81" s="5" t="inlineStr"/>
+      <c r="M81" s="5" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="P81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5485,12 +5493,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5499,7 +5507,7 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>272.48</v>
+        <v>269.8</v>
       </c>
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr"/>
@@ -5510,12 +5518,8 @@
       <c r="K82" s="5" t="inlineStr"/>
       <c r="L82" s="5" t="inlineStr"/>
       <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr"/>
       <c r="P82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5568,7 +5572,9 @@
       <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="5" t="inlineStr"/>
       <c r="L83" s="5" t="inlineStr"/>
-      <c r="M83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="n">
+        <v>0.9588</v>
+      </c>
       <c r="N83" s="5" t="n">
         <v>0.9611</v>
       </c>
@@ -5973,7 +5979,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6040,12 +6046,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6054,7 +6060,7 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>0.9567</v>
@@ -6174,12 +6180,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6188,7 +6194,7 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0.9567</v>
@@ -6416,7 +6422,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -6483,7 +6489,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6550,7 +6556,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6617,7 +6623,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7208,7 +7214,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7275,7 +7281,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7458,41 +7464,51 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Edenvale Solar Park</t>
+          <t>Grosvenor 2</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>180</v>
+        <v>15.205</v>
       </c>
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="5" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="5" t="inlineStr"/>
-      <c r="K113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="L113" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="O113" s="5" t="inlineStr"/>
       <c r="P113" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="Q113" s="5" t="inlineStr"/>
       <c r="R113" s="5" t="n">
@@ -7500,10 +7516,10 @@
       </c>
       <c r="S113" s="5" t="inlineStr"/>
       <c r="T113" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.018</v>
       </c>
       <c r="U113" s="6" t="n">
-        <v>-0.26</v>
+        <v>-1.8</v>
       </c>
       <c r="V113" s="5" t="inlineStr"/>
       <c r="W113" s="6" t="inlineStr"/>
@@ -7511,12 +7527,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 2</t>
+          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -7525,10 +7541,12 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>15.205</v>
+        <v>21.287</v>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
-      <c r="F114" s="5" t="inlineStr"/>
+      <c r="F114" s="5" t="n">
+        <v>1.0727</v>
+      </c>
       <c r="G114" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -7574,53 +7592,41 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
+          <t>Edenvale Solar Park</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>21.287</v>
+        <v>180</v>
       </c>
       <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="n">
-        <v>1.0727</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="I115" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="K115" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="5" t="inlineStr"/>
+      <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="O115" s="5" t="inlineStr"/>
       <c r="P115" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="Q115" s="5" t="inlineStr"/>
       <c r="R115" s="5" t="n">
@@ -7628,10 +7634,10 @@
       </c>
       <c r="S115" s="5" t="inlineStr"/>
       <c r="T115" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0026</v>
       </c>
       <c r="U115" s="6" t="n">
-        <v>-1.8</v>
+        <v>-0.26</v>
       </c>
       <c r="V115" s="5" t="inlineStr"/>
       <c r="W115" s="6" t="inlineStr"/>
@@ -7926,7 +7932,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -7940,7 +7946,7 @@
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
@@ -7949,9 +7955,15 @@
       <c r="I121" s="5" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="5" t="inlineStr"/>
-      <c r="L121" s="5" t="inlineStr"/>
-      <c r="M121" s="5" t="inlineStr"/>
-      <c r="N121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -7973,7 +7985,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7987,7 +7999,7 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>159</v>
+        <v>310</v>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr"/>
@@ -7996,15 +8008,9 @@
       <c r="I122" s="5" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="5" t="inlineStr"/>
-      <c r="L122" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="N122" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="L122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr"/>
       <c r="O122" s="5" t="inlineStr"/>
       <c r="P122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -8213,41 +8219,45 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t>Warwick Solar Farm 2</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="5" t="inlineStr"/>
-      <c r="K126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L126" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="O126" s="5" t="inlineStr"/>
       <c r="P126" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="Q126" s="5" t="inlineStr"/>
       <c r="R126" s="5" t="n">
@@ -8255,10 +8265,10 @@
       </c>
       <c r="S126" s="5" t="inlineStr"/>
       <c r="T126" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="U126" s="6" t="n">
-        <v>0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="V126" s="5" t="inlineStr"/>
       <c r="W126" s="6" t="inlineStr"/>
@@ -8266,45 +8276,41 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Warwick Solar Farm 2</t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="J127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="O127" s="5" t="inlineStr"/>
       <c r="P127" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="Q127" s="5" t="inlineStr"/>
       <c r="R127" s="5" t="n">
@@ -8312,10 +8318,10 @@
       </c>
       <c r="S127" s="5" t="inlineStr"/>
       <c r="T127" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="U127" s="6" t="n">
-        <v>-0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V127" s="5" t="inlineStr"/>
       <c r="W127" s="6" t="inlineStr"/>
@@ -8323,12 +8329,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warwick Solar Farm 1 </t>
+          <t>Maryrorough Solar Farm</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -8337,13 +8343,15 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="J128" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8380,12 +8388,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Maryrorough Solar Farm</t>
+          <t>Yarranlea Solar Farm</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -8394,7 +8402,7 @@
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="5" t="inlineStr"/>
@@ -8439,12 +8447,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Yarranlea Solar Farm</t>
+          <t xml:space="preserve">Warwick Solar Farm 1 </t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8453,15 +8461,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="I130" s="5" t="inlineStr"/>
       <c r="J130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8630,10 +8636,14 @@
           <t>Pioneer Sugar Mill</t>
         </is>
       </c>
-      <c r="C133" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>68</v>
+      </c>
       <c r="E133" s="5" t="n">
         <v>1.0872</v>
       </c>
@@ -8841,9 +8851,15 @@
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr"/>
-      <c r="K136" s="5" t="inlineStr"/>
-      <c r="L136" s="5" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr"/>
+      <c r="K136" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="M136" s="5" t="n">
+        <v>0.9751</v>
+      </c>
       <c r="N136" s="5" t="n">
         <v>0.9823</v>
       </c>
@@ -8933,70 +8949,62 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>QLD1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr"/>
+          <t>Supernode BESS</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D138" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>337.4</v>
+      </c>
+      <c r="E138" s="5" t="inlineStr"/>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="inlineStr"/>
       <c r="O138" s="5" t="inlineStr"/>
       <c r="P138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" s="5" t="inlineStr"/>
+      <c r="Q138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="R138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S138" s="5" t="inlineStr"/>
+      <c r="S138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="T138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U138" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="5" t="inlineStr"/>
-      <c r="W138" s="6" t="inlineStr"/>
+      <c r="V138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>SNB01</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9051,57 +9059,65 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>DG_QLD1</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Supernode BESS</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n"/>
       <c r="D140" s="4" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="E140" s="5" t="inlineStr"/>
-      <c r="F140" s="5" t="inlineStr"/>
-      <c r="G140" s="5" t="inlineStr"/>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
-      <c r="J140" s="5" t="inlineStr"/>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="5" t="inlineStr"/>
-      <c r="M140" s="5" t="inlineStr"/>
-      <c r="N140" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O140" s="5" t="inlineStr"/>
       <c r="P140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q140" s="5" t="inlineStr"/>
       <c r="R140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S140" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S140" s="5" t="inlineStr"/>
       <c r="T140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U140" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="V140" s="5" t="inlineStr"/>
+      <c r="W140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -9887,88 +9903,52 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>VICMILL1</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>Victoria Mill</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
+          <t>KIDSPHL2</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C154" s="3" t="n"/>
       <c r="D154" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="F154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="I154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E154" s="5" t="inlineStr"/>
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr"/>
+      <c r="K154" s="5" t="inlineStr"/>
+      <c r="L154" s="5" t="inlineStr"/>
+      <c r="M154" s="5" t="inlineStr"/>
+      <c r="N154" s="5" t="inlineStr"/>
       <c r="O154" s="5" t="inlineStr"/>
-      <c r="P154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
+      <c r="P154" s="5" t="inlineStr"/>
       <c r="Q154" s="5" t="inlineStr"/>
       <c r="R154" s="5" t="n">
-        <v>1.1403</v>
+        <v>1.0394</v>
       </c>
       <c r="S154" s="5" t="inlineStr"/>
-      <c r="T154" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="T154" s="5" t="inlineStr"/>
+      <c r="U154" s="6" t="inlineStr"/>
       <c r="V154" s="5" t="inlineStr"/>
       <c r="W154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>SUNCOAST</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>Suncoast Gold Macadamias</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr"/>
+          <t>KIDSPHL1</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C155" s="3" t="n"/>
       <c r="D155" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" s="5" t="n">
-        <v>1.0124</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E155" s="5" t="inlineStr"/>
       <c r="F155" s="5" t="inlineStr"/>
       <c r="G155" s="5" t="inlineStr"/>
       <c r="H155" s="5" t="inlineStr"/>
@@ -9981,7 +9961,9 @@
       <c r="O155" s="5" t="inlineStr"/>
       <c r="P155" s="5" t="inlineStr"/>
       <c r="Q155" s="5" t="inlineStr"/>
-      <c r="R155" s="5" t="inlineStr"/>
+      <c r="R155" s="5" t="n">
+        <v>1.0394</v>
+      </c>
       <c r="S155" s="5" t="inlineStr"/>
       <c r="T155" s="5" t="inlineStr"/>
       <c r="U155" s="6" t="inlineStr"/>
@@ -9991,84 +9973,92 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>STHBKTEC</t>
+          <t>VICMILL1</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Southbank Institute Of Technology Unit 1 Plant</t>
+          <t>Victoria Mill</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1.0141</v>
+        <v>1.1403</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>1.0125</v>
+        <v>1.1403</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1.0129</v>
+        <v>1.1403</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>1.0122</v>
-      </c>
-      <c r="I156" s="5" t="inlineStr"/>
-      <c r="J156" s="5" t="inlineStr"/>
-      <c r="K156" s="5" t="inlineStr"/>
-      <c r="L156" s="5" t="inlineStr"/>
-      <c r="M156" s="5" t="inlineStr"/>
-      <c r="N156" s="5" t="inlineStr"/>
+        <v>1.1403</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="M156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="N156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="O156" s="5" t="inlineStr"/>
-      <c r="P156" s="5" t="inlineStr"/>
+      <c r="P156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="Q156" s="5" t="inlineStr"/>
-      <c r="R156" s="5" t="inlineStr"/>
+      <c r="R156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="S156" s="5" t="inlineStr"/>
-      <c r="T156" s="5" t="inlineStr"/>
-      <c r="U156" s="6" t="inlineStr"/>
+      <c r="T156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="V156" s="5" t="inlineStr"/>
       <c r="W156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>SUNCOAST</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Roghan Road LFG Power Plant</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
+          <t>Suncoast Gold Macadamias</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n"/>
       <c r="D157" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1.0057</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>1.0049</v>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>1.0044</v>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>1.0042</v>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>1.0042</v>
-      </c>
+        <v>1.0124</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr"/>
       <c r="J157" s="5" t="inlineStr"/>
       <c r="K157" s="5" t="inlineStr"/>
       <c r="L157" s="5" t="inlineStr"/>
@@ -10087,37 +10077,35 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>STHBKTEC</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Whitwood Road Renewable Energy Facility</t>
+          <t>Southbank Institute Of Technology Unit 1 Plant</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0141</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0125</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0129</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>1.0006</v>
-      </c>
+        <v>1.0122</v>
+      </c>
+      <c r="I158" s="5" t="inlineStr"/>
       <c r="J158" s="5" t="inlineStr"/>
       <c r="K158" s="5" t="inlineStr"/>
       <c r="L158" s="5" t="inlineStr"/>
@@ -10136,12 +10124,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Rochedale Renewable Energy Facility</t>
+          <t>Whitwood Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10150,22 +10138,22 @@
         </is>
       </c>
       <c r="D159" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="J159" s="5" t="inlineStr"/>
       <c r="K159" s="5" t="inlineStr"/>
@@ -10185,40 +10173,38 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>MACKAYGT</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>MACKAY GAS TURBINE</t>
+          <t>Rochedale Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1.055</v>
+        <v>1.0067</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0091</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.9577</v>
+        <v>1.0114</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>0.8863</v>
+        <v>1.0123</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>0.9062</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>0.8893</v>
-      </c>
+        <v>1.0121</v>
+      </c>
+      <c r="J160" s="5" t="inlineStr"/>
       <c r="K160" s="5" t="inlineStr"/>
       <c r="L160" s="5" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
@@ -10236,43 +10222,39 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>DAANDINE</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Daandine Power Station</t>
+          <t>Roghan Road LFG Power Plant</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D161" s="4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0.9747</v>
+        <v>1.0057</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0.9717</v>
+        <v>1.0049</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.9816</v>
+        <v>1.0044</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0.9867</v>
+        <v>1.0042</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="K161" s="5" t="n">
-        <v>0.9774</v>
-      </c>
+        <v>1.0042</v>
+      </c>
+      <c r="J161" s="5" t="inlineStr"/>
+      <c r="K161" s="5" t="inlineStr"/>
       <c r="L161" s="5" t="inlineStr"/>
       <c r="M161" s="5" t="inlineStr"/>
       <c r="N161" s="5" t="inlineStr"/>
@@ -10289,49 +10271,43 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>WIVENSH</t>
+          <t>MACKAYGT</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>WIVENHOE SMALL HYDRO</t>
+          <t>MACKAY GAS TURBINE</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.055</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.9951</v>
+        <v>0.9737</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.999</v>
+        <v>0.9577</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.8863</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>1.0043</v>
+        <v>0.9062</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>1.0027</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>0.9985000000000001</v>
-      </c>
+        <v>0.8893</v>
+      </c>
+      <c r="K162" s="5" t="inlineStr"/>
+      <c r="L162" s="5" t="inlineStr"/>
+      <c r="M162" s="5" t="inlineStr"/>
       <c r="N162" s="5" t="inlineStr"/>
       <c r="O162" s="5" t="inlineStr"/>
       <c r="P162" s="5" t="inlineStr"/>
@@ -10346,32 +10322,46 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>DAANDINE</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Bouldercombe Battery Project</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D163" s="3" t="inlineStr"/>
-      <c r="E163" s="5" t="inlineStr"/>
-      <c r="F163" s="5" t="inlineStr"/>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr"/>
-      <c r="I163" s="5" t="inlineStr"/>
-      <c r="J163" s="5" t="inlineStr"/>
-      <c r="K163" s="5" t="inlineStr"/>
+          <t>Daandine Power Station</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.9717</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>0.9774</v>
+      </c>
       <c r="L163" s="5" t="inlineStr"/>
-      <c r="M163" s="5" t="n">
-        <v>0.9198</v>
-      </c>
-      <c r="N163" s="5" t="n">
-        <v>0.9166</v>
-      </c>
+      <c r="M163" s="5" t="inlineStr"/>
+      <c r="N163" s="5" t="inlineStr"/>
       <c r="O163" s="5" t="inlineStr"/>
       <c r="P163" s="5" t="inlineStr"/>
       <c r="Q163" s="5" t="inlineStr"/>
@@ -10385,36 +10375,50 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>WIVENSH</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Chinchilla BESS</t>
+          <t>WIVENHOE SMALL HYDRO</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="E164" s="5" t="inlineStr"/>
-      <c r="F164" s="5" t="inlineStr"/>
-      <c r="G164" s="5" t="inlineStr"/>
-      <c r="H164" s="5" t="inlineStr"/>
-      <c r="I164" s="5" t="inlineStr"/>
-      <c r="J164" s="5" t="inlineStr"/>
-      <c r="K164" s="5" t="inlineStr"/>
-      <c r="L164" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.9951</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="M164" s="5" t="n">
-        <v>0.9588</v>
-      </c>
-      <c r="N164" s="5" t="n">
-        <v>0.9611</v>
-      </c>
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="N164" s="5" t="inlineStr"/>
       <c r="O164" s="5" t="inlineStr"/>
       <c r="P164" s="5" t="inlineStr"/>
       <c r="Q164" s="5" t="inlineStr"/>
@@ -10424,96 +10428,6 @@
       <c r="U164" s="6" t="inlineStr"/>
       <c r="V164" s="5" t="inlineStr"/>
       <c r="W164" s="6" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>WDBESSG1</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="E165" s="5" t="inlineStr"/>
-      <c r="F165" s="5" t="inlineStr"/>
-      <c r="G165" s="5" t="inlineStr"/>
-      <c r="H165" s="5" t="inlineStr"/>
-      <c r="I165" s="5" t="inlineStr"/>
-      <c r="J165" s="5" t="inlineStr"/>
-      <c r="K165" s="5" t="inlineStr"/>
-      <c r="L165" s="5" t="inlineStr"/>
-      <c r="M165" s="5" t="n">
-        <v>0.9586</v>
-      </c>
-      <c r="N165" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="O165" s="5" t="inlineStr"/>
-      <c r="P165" s="5" t="inlineStr"/>
-      <c r="Q165" s="5" t="inlineStr"/>
-      <c r="R165" s="5" t="inlineStr"/>
-      <c r="S165" s="5" t="inlineStr"/>
-      <c r="T165" s="5" t="inlineStr"/>
-      <c r="U165" s="6" t="inlineStr"/>
-      <c r="V165" s="5" t="inlineStr"/>
-      <c r="W165" s="6" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>WANDBG1</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>Wandoan BESS</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="E166" s="5" t="inlineStr"/>
-      <c r="F166" s="5" t="inlineStr"/>
-      <c r="G166" s="5" t="inlineStr"/>
-      <c r="H166" s="5" t="inlineStr"/>
-      <c r="I166" s="5" t="inlineStr"/>
-      <c r="J166" s="5" t="inlineStr"/>
-      <c r="K166" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v>0.9751</v>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v>0.9823</v>
-      </c>
-      <c r="O166" s="5" t="inlineStr"/>
-      <c r="P166" s="5" t="inlineStr"/>
-      <c r="Q166" s="5" t="inlineStr"/>
-      <c r="R166" s="5" t="inlineStr"/>
-      <c r="S166" s="5" t="inlineStr"/>
-      <c r="T166" s="5" t="inlineStr"/>
-      <c r="U166" s="6" t="inlineStr"/>
-      <c r="V166" s="5" t="inlineStr"/>
-      <c r="W166" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10526,7 +10440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10798,7 +10712,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -10838,7 +10752,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -11046,7 +10960,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
@@ -11088,7 +11002,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
@@ -11238,14 +11152,18 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>1.0107</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
       <c r="E17" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11320,18 +11238,14 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n">
-        <v>1.0107</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0.9715</v>
-      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11404,7 +11318,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -11430,7 +11344,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
@@ -11576,7 +11490,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -11622,7 +11536,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -11742,7 +11656,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -11788,7 +11702,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -11834,7 +11748,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -11872,7 +11786,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -11910,7 +11824,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -11956,7 +11870,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -12002,7 +11916,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -12048,7 +11962,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -12278,7 +12192,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
@@ -12295,16 +12209,20 @@
       <c r="M42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="O42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="n">
+        <v>0.9247</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr"/>
@@ -12321,15 +12239,11 @@
       <c r="M43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N43" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P43" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="P43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12410,7 +12324,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -12502,7 +12416,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -12548,7 +12462,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -12640,7 +12554,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -12686,7 +12600,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -12732,7 +12646,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
@@ -12760,7 +12674,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
@@ -12825,7 +12739,9 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="n">
+        <v>0.9198</v>
+      </c>
       <c r="K56" s="5" t="n">
         <v>0.9166</v>
       </c>
@@ -12994,7 +12910,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -13040,7 +12956,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -13166,7 +13082,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -13258,7 +13174,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -13338,7 +13254,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
@@ -13346,25 +13262,13 @@
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="M69" s="5" t="inlineStr"/>
       <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="n">
         <v>0.9574</v>
@@ -13410,7 +13314,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
@@ -13446,7 +13350,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
@@ -13454,13 +13358,25 @@
       <c r="D72" s="5" t="inlineStr"/>
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="n">
         <v>0.9574</v>
@@ -13496,7 +13412,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -13542,7 +13458,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -13588,7 +13504,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -13680,7 +13596,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -13798,7 +13714,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
@@ -13809,9 +13725,15 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr"/>
-      <c r="K81" s="5" t="inlineStr"/>
-      <c r="L81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="M81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -13828,7 +13750,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
@@ -13840,12 +13762,8 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr"/>
       <c r="M82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -13873,7 +13791,9 @@
       <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
+      <c r="J83" s="5" t="n">
+        <v>0.9588</v>
+      </c>
       <c r="K83" s="5" t="n">
         <v>0.9611</v>
       </c>
@@ -14136,7 +14056,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -14182,7 +14102,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -14274,7 +14194,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -14428,7 +14348,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -14474,7 +14394,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -14520,7 +14440,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -14566,7 +14486,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -14968,7 +14888,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -15014,7 +14934,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -15134,28 +15054,38 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr"/>
-      <c r="D113" s="5" t="inlineStr"/>
-      <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="5" t="inlineStr"/>
+      <c r="D113" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="I113" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="N113" s="5" t="inlineStr"/>
       <c r="O113" s="5" t="n">
@@ -15166,11 +15096,13 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr"/>
-      <c r="C114" s="5" t="inlineStr"/>
+      <c r="C114" s="5" t="n">
+        <v>1.0727</v>
+      </c>
       <c r="D114" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -15208,40 +15140,28 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr"/>
-      <c r="C115" s="5" t="n">
-        <v>1.0727</v>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="C115" s="5" t="inlineStr"/>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr"/>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="N115" s="5" t="inlineStr"/>
       <c r="O115" s="5" t="n">
@@ -15430,7 +15350,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr"/>
@@ -15440,9 +15360,15 @@
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="5" t="inlineStr"/>
-      <c r="K121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15456,7 +15382,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr"/>
@@ -15466,15 +15392,9 @@
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="5" t="inlineStr"/>
+      <c r="K122" s="5" t="inlineStr"/>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15612,7 +15532,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr"/>
@@ -15620,20 +15540,24 @@
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="I126" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="5" t="n">
@@ -15644,7 +15568,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr"/>
@@ -15652,24 +15576,20 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
-      <c r="G127" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="N127" s="5" t="inlineStr"/>
       <c r="O127" s="5" t="n">
@@ -15680,14 +15600,16 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr"/>
       <c r="C128" s="5" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="inlineStr"/>
+      <c r="F128" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="G128" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -15716,7 +15638,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr"/>
@@ -15754,16 +15676,14 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr"/>
       <c r="C130" s="5" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -16021,9 +15941,15 @@
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="5" t="inlineStr"/>
       <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>0.9751</v>
+      </c>
       <c r="K136" s="5" t="n">
         <v>0.9823</v>
       </c>
@@ -16076,53 +16002,37 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>SNB02</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr"/>
+      <c r="C138" s="5" t="inlineStr"/>
+      <c r="D138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr"/>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr"/>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P138" s="5" t="inlineStr"/>
+      <c r="P138" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>SNB01</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr"/>
@@ -16152,32 +16062,48 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr"/>
-      <c r="C140" s="5" t="inlineStr"/>
-      <c r="D140" s="5" t="inlineStr"/>
-      <c r="E140" s="5" t="inlineStr"/>
-      <c r="F140" s="5" t="inlineStr"/>
-      <c r="G140" s="5" t="inlineStr"/>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
-      <c r="J140" s="5" t="inlineStr"/>
-      <c r="K140" s="5" t="inlineStr"/>
+          <t>DG_QLD1</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N140" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P140" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -16690,58 +16616,34 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>VICMILL1</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="C154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="D154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="E154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="F154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="I154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
+          <t>KIDSPHL2</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr"/>
+      <c r="C154" s="5" t="inlineStr"/>
+      <c r="D154" s="5" t="inlineStr"/>
+      <c r="E154" s="5" t="inlineStr"/>
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="5" t="inlineStr"/>
+      <c r="K154" s="5" t="inlineStr"/>
       <c r="L154" s="5" t="inlineStr"/>
-      <c r="M154" s="5" t="n">
-        <v>1.1403</v>
-      </c>
+      <c r="M154" s="5" t="inlineStr"/>
       <c r="N154" s="5" t="inlineStr"/>
       <c r="O154" s="5" t="n">
-        <v>1.1403</v>
+        <v>1.0394</v>
       </c>
       <c r="P154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>SUNCOAST</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="n">
-        <v>1.0124</v>
-      </c>
+          <t>KIDSPHL1</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr"/>
       <c r="C155" s="5" t="inlineStr"/>
       <c r="D155" s="5" t="inlineStr"/>
       <c r="E155" s="5" t="inlineStr"/>
@@ -16754,60 +16656,70 @@
       <c r="L155" s="5" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
       <c r="N155" s="5" t="inlineStr"/>
-      <c r="O155" s="5" t="inlineStr"/>
+      <c r="O155" s="5" t="n">
+        <v>1.0394</v>
+      </c>
       <c r="P155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>STHBKTEC</t>
+          <t>VICMILL1</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>1.0141</v>
+        <v>1.1403</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>1.0125</v>
+        <v>1.1403</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>1.0129</v>
+        <v>1.1403</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1.0122</v>
-      </c>
-      <c r="F156" s="5" t="inlineStr"/>
-      <c r="G156" s="5" t="inlineStr"/>
-      <c r="H156" s="5" t="inlineStr"/>
-      <c r="I156" s="5" t="inlineStr"/>
-      <c r="J156" s="5" t="inlineStr"/>
-      <c r="K156" s="5" t="inlineStr"/>
+        <v>1.1403</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="L156" s="5" t="inlineStr"/>
-      <c r="M156" s="5" t="inlineStr"/>
+      <c r="M156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="N156" s="5" t="inlineStr"/>
-      <c r="O156" s="5" t="inlineStr"/>
+      <c r="O156" s="5" t="n">
+        <v>1.1403</v>
+      </c>
       <c r="P156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>SUNCOAST</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>1.0057</v>
-      </c>
-      <c r="C157" s="5" t="n">
-        <v>1.0049</v>
-      </c>
-      <c r="D157" s="5" t="n">
-        <v>1.0044</v>
-      </c>
-      <c r="E157" s="5" t="n">
-        <v>1.0042</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>1.0042</v>
-      </c>
+        <v>1.0124</v>
+      </c>
+      <c r="C157" s="5" t="inlineStr"/>
+      <c r="D157" s="5" t="inlineStr"/>
+      <c r="E157" s="5" t="inlineStr"/>
+      <c r="F157" s="5" t="inlineStr"/>
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="inlineStr"/>
@@ -16822,24 +16734,22 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>STHBKTEC</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0141</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0125</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0129</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>1.0006</v>
-      </c>
+        <v>1.0122</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr"/>
       <c r="G158" s="5" t="inlineStr"/>
       <c r="H158" s="5" t="inlineStr"/>
       <c r="I158" s="5" t="inlineStr"/>
@@ -16854,23 +16764,23 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
       <c r="H159" s="5" t="inlineStr"/>
@@ -16886,27 +16796,25 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>MACKAYGT</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>1.055</v>
+        <v>1.0067</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>0.9737</v>
+        <v>1.0091</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>0.9577</v>
+        <v>1.0114</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0.8863</v>
+        <v>1.0123</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.9062</v>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>0.8893</v>
-      </c>
+        <v>1.0121</v>
+      </c>
+      <c r="G160" s="5" t="inlineStr"/>
       <c r="H160" s="5" t="inlineStr"/>
       <c r="I160" s="5" t="inlineStr"/>
       <c r="J160" s="5" t="inlineStr"/>
@@ -16920,30 +16828,26 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>DAANDINE</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>0.9747</v>
+        <v>1.0057</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>0.9717</v>
+        <v>1.0049</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>0.9816</v>
+        <v>1.0044</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0.9867</v>
+        <v>1.0042</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>0.9774</v>
-      </c>
+        <v>1.0042</v>
+      </c>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr"/>
       <c r="K161" s="5" t="inlineStr"/>
@@ -16956,36 +16860,30 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>WIVENSH</t>
+          <t>MACKAYGT</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.055</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>0.9951</v>
+        <v>0.9737</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>0.999</v>
+        <v>0.9577</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.9968</v>
+        <v>0.8863</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>1.0043</v>
+        <v>0.9062</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1.0027</v>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>0.9985000000000001</v>
-      </c>
+        <v>0.8893</v>
+      </c>
+      <c r="H162" s="5" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr"/>
+      <c r="J162" s="5" t="inlineStr"/>
       <c r="K162" s="5" t="inlineStr"/>
       <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="inlineStr"/>
@@ -16996,23 +16894,33 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr"/>
-      <c r="C163" s="5" t="inlineStr"/>
-      <c r="D163" s="5" t="inlineStr"/>
-      <c r="E163" s="5" t="inlineStr"/>
-      <c r="F163" s="5" t="inlineStr"/>
-      <c r="G163" s="5" t="inlineStr"/>
-      <c r="H163" s="5" t="inlineStr"/>
+          <t>DAANDINE</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>0.9717</v>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.9774</v>
+      </c>
       <c r="I163" s="5" t="inlineStr"/>
-      <c r="J163" s="5" t="n">
-        <v>0.9198</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0.9166</v>
-      </c>
+      <c r="J163" s="5" t="inlineStr"/>
+      <c r="K163" s="5" t="inlineStr"/>
       <c r="L163" s="5" t="inlineStr"/>
       <c r="M163" s="5" t="inlineStr"/>
       <c r="N163" s="5" t="inlineStr"/>
@@ -17022,87 +16930,45 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="inlineStr"/>
-      <c r="C164" s="5" t="inlineStr"/>
-      <c r="D164" s="5" t="inlineStr"/>
-      <c r="E164" s="5" t="inlineStr"/>
-      <c r="F164" s="5" t="inlineStr"/>
-      <c r="G164" s="5" t="inlineStr"/>
-      <c r="H164" s="5" t="inlineStr"/>
-      <c r="I164" s="5" t="inlineStr"/>
+          <t>WIVENSH</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>0.9951</v>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="J164" s="5" t="n">
-        <v>0.9588</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>0.9611</v>
-      </c>
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="K164" s="5" t="inlineStr"/>
       <c r="L164" s="5" t="inlineStr"/>
       <c r="M164" s="5" t="inlineStr"/>
       <c r="N164" s="5" t="inlineStr"/>
       <c r="O164" s="5" t="inlineStr"/>
       <c r="P164" s="5" t="inlineStr"/>
     </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>WDBESSG1</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr"/>
-      <c r="C165" s="5" t="inlineStr"/>
-      <c r="D165" s="5" t="inlineStr"/>
-      <c r="E165" s="5" t="inlineStr"/>
-      <c r="F165" s="5" t="inlineStr"/>
-      <c r="G165" s="5" t="inlineStr"/>
-      <c r="H165" s="5" t="inlineStr"/>
-      <c r="I165" s="5" t="inlineStr"/>
-      <c r="J165" s="5" t="n">
-        <v>0.9586</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="L165" s="5" t="inlineStr"/>
-      <c r="M165" s="5" t="inlineStr"/>
-      <c r="N165" s="5" t="inlineStr"/>
-      <c r="O165" s="5" t="inlineStr"/>
-      <c r="P165" s="5" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>WANDBG1</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr"/>
-      <c r="C166" s="5" t="inlineStr"/>
-      <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="5" t="inlineStr"/>
-      <c r="F166" s="5" t="inlineStr"/>
-      <c r="G166" s="5" t="inlineStr"/>
-      <c r="H166" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="J166" s="5" t="n">
-        <v>0.9751</v>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>0.9823</v>
-      </c>
-      <c r="L166" s="5" t="inlineStr"/>
-      <c r="M166" s="5" t="inlineStr"/>
-      <c r="N166" s="5" t="inlineStr"/>
-      <c r="O166" s="5" t="inlineStr"/>
-      <c r="P166" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B166">
+  <conditionalFormatting sqref="B2:B164">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -17114,7 +16980,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C166">
+  <conditionalFormatting sqref="C2:C164">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -17126,7 +16992,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D166">
+  <conditionalFormatting sqref="D2:D164">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -17138,7 +17004,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E166">
+  <conditionalFormatting sqref="E2:E164">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -17150,7 +17016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F166">
+  <conditionalFormatting sqref="F2:F164">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -17162,7 +17028,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G166">
+  <conditionalFormatting sqref="G2:G164">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -17174,7 +17040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H166">
+  <conditionalFormatting sqref="H2:H164">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -17186,7 +17052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I166">
+  <conditionalFormatting sqref="I2:I164">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -17198,7 +17064,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J166">
+  <conditionalFormatting sqref="J2:J164">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -17210,7 +17076,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K166">
+  <conditionalFormatting sqref="K2:K164">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -17222,7 +17088,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L166">
+  <conditionalFormatting sqref="M2:M164">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -17234,44 +17100,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M166">
+  <conditionalFormatting sqref="O2:O164">
     <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N166">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O166">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P166">
-    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -17409,7 +17239,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -17438,7 +17268,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -17554,12 +17384,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -17583,12 +17413,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -17699,12 +17529,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17728,12 +17558,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -17815,12 +17645,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17873,12 +17703,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -17975,7 +17805,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -18033,7 +17863,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -18294,7 +18124,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -18323,7 +18153,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -18381,12 +18211,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -18410,12 +18240,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -18526,12 +18356,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>DDPS1</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Darling Downs Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>57.75</v>
+        <v>167</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
@@ -920,12 +920,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>167</v>
+        <v>57.75</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>50</v>
+        <v>20.97</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1296,12 +1296,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20.97</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1544,17 +1544,13 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>92.5</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="n">
-        <v>1.0107</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.9715</v>
-      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1658,12 +1654,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1672,13 +1668,17 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>92.5</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>1.0107</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.9715</v>
+      </c>
       <c r="H19" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -1780,7 +1780,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9648</v>
@@ -2124,7 +2124,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0.9648</v>
@@ -2307,12 +2307,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek 2</t>
+          <t>Oaky Creek Power Station</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>1.0373</v>
@@ -2374,12 +2374,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek Power Station</t>
+          <t>Oaky Creek 2</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1.0373</v>
@@ -2441,7 +2441,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2449,10 +2449,8 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v/>
       </c>
       <c r="D32" s="4" t="n">
         <v>30</v>
@@ -2496,7 +2494,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2504,7 +2502,11 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n">
         <v>30</v>
       </c>
@@ -2547,7 +2549,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2614,7 +2616,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2681,7 +2683,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2748,7 +2750,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3083,7 +3085,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3093,11 +3095,11 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr"/>
@@ -3113,32 +3115,24 @@
       <c r="P42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q42" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S42" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U42" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V42" s="5" t="n">
-        <v>-0.0043</v>
-      </c>
-      <c r="W42" s="6" t="n">
-        <v>-0.46</v>
-      </c>
+      <c r="V42" s="5" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3148,11 +3142,11 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr"/>
@@ -3168,19 +3162,27 @@
       <c r="P43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="R43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="n">
+        <v>0.9247</v>
+      </c>
       <c r="T43" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U43" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V43" s="5" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
+      <c r="V43" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3307,12 +3309,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Gladstone Power Station</t>
+          <t>GLADSTONE POWER STATION</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3321,7 +3323,7 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0.9855</v>
@@ -3441,12 +3443,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GLADSTONE POWER STATION</t>
+          <t>Gladstone Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3455,7 +3457,7 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.9855</v>
@@ -3508,7 +3510,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3642,7 +3644,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3709,7 +3711,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3776,7 +3778,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3790,7 +3792,7 @@
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>345.5</v>
+        <v>103.5</v>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="inlineStr"/>
@@ -3825,7 +3827,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3839,7 +3841,7 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>103.5</v>
+        <v>345.5</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
@@ -4212,7 +4214,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4279,7 +4281,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4468,7 +4470,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4482,7 +4484,7 @@
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>1.0156</v>
@@ -4602,7 +4604,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4616,7 +4618,7 @@
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>1.0156</v>
@@ -4724,7 +4726,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4745,20 +4747,36 @@
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr"/>
-      <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="O69" s="5" t="inlineStr"/>
-      <c r="P69" s="5" t="inlineStr"/>
+      <c r="P69" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S69" s="5" t="inlineStr"/>
-      <c r="T69" s="5" t="inlineStr"/>
-      <c r="U69" s="6" t="inlineStr"/>
+      <c r="T69" s="5" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="U69" s="6" t="n">
+        <v>-2.44</v>
+      </c>
       <c r="V69" s="5" t="inlineStr"/>
       <c r="W69" s="6" t="inlineStr"/>
     </row>
@@ -4822,21 +4840,21 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park Battery</t>
+          <t>Kennedy Energy Park</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="5" t="inlineStr"/>
@@ -4879,57 +4897,41 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park</t>
+          <t>Kennedy Energy Park Battery</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="P72" s="5" t="inlineStr"/>
       <c r="Q72" s="5" t="inlineStr"/>
       <c r="R72" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S72" s="5" t="inlineStr"/>
-      <c r="T72" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="U72" s="6" t="n">
-        <v>-2.44</v>
-      </c>
+      <c r="T72" s="5" t="inlineStr"/>
+      <c r="U72" s="6" t="inlineStr"/>
       <c r="V72" s="5" t="inlineStr"/>
       <c r="W72" s="6" t="inlineStr"/>
     </row>
@@ -4983,7 +4985,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5050,7 +5052,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5064,7 +5066,7 @@
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>1.069</v>
@@ -5117,7 +5119,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5251,7 +5253,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5265,7 +5267,7 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>1.069</v>
@@ -5432,12 +5434,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -5446,7 +5448,7 @@
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>272.48</v>
+        <v>269.8</v>
       </c>
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="5" t="inlineStr"/>
@@ -5456,15 +5458,9 @@
       <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="5" t="inlineStr"/>
-      <c r="M81" s="5" t="n">
-        <v>0.9586</v>
-      </c>
-      <c r="N81" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="O81" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
       <c r="P81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5493,12 +5489,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -5507,7 +5503,7 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>269.8</v>
+        <v>272.48</v>
       </c>
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="5" t="inlineStr"/>
@@ -5517,9 +5513,15 @@
       <c r="J82" s="5" t="inlineStr"/>
       <c r="K82" s="5" t="inlineStr"/>
       <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr"/>
-      <c r="O82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="P82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -5979,7 +5981,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6046,12 +6048,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6060,7 +6062,7 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>0.9567</v>
@@ -6180,12 +6182,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6194,7 +6196,7 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>0.9567</v>
@@ -6422,7 +6424,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -6489,7 +6491,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6556,7 +6558,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6623,7 +6625,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7214,7 +7216,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7281,7 +7283,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7464,51 +7466,41 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 2</t>
+          <t>Edenvale Solar Park</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>15.205</v>
+        <v>180</v>
       </c>
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="I113" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="5" t="inlineStr"/>
+      <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="O113" s="5" t="inlineStr"/>
       <c r="P113" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="Q113" s="5" t="inlineStr"/>
       <c r="R113" s="5" t="n">
@@ -7516,10 +7508,10 @@
       </c>
       <c r="S113" s="5" t="inlineStr"/>
       <c r="T113" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0026</v>
       </c>
       <c r="U113" s="6" t="n">
-        <v>-1.8</v>
+        <v>-0.26</v>
       </c>
       <c r="V113" s="5" t="inlineStr"/>
       <c r="W113" s="6" t="inlineStr"/>
@@ -7527,12 +7519,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
+          <t>Grosvenor 2</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -7541,12 +7533,10 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>21.287</v>
+        <v>15.205</v>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
-      <c r="F114" s="5" t="n">
-        <v>1.0727</v>
-      </c>
+      <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -7592,41 +7582,53 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Edenvale Solar Park</t>
+          <t>Grosvenor 1 Waste Coal Mine Gas Power Station</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>180</v>
+        <v>21.287</v>
       </c>
       <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr"/>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="5" t="inlineStr"/>
-      <c r="J115" s="5" t="inlineStr"/>
-      <c r="K115" s="5" t="inlineStr"/>
+      <c r="F115" s="5" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="L115" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="O115" s="5" t="inlineStr"/>
       <c r="P115" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="Q115" s="5" t="inlineStr"/>
       <c r="R115" s="5" t="n">
@@ -7634,10 +7636,10 @@
       </c>
       <c r="S115" s="5" t="inlineStr"/>
       <c r="T115" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.018</v>
       </c>
       <c r="U115" s="6" t="n">
-        <v>-0.26</v>
+        <v>-1.8</v>
       </c>
       <c r="V115" s="5" t="inlineStr"/>
       <c r="W115" s="6" t="inlineStr"/>
@@ -7932,7 +7934,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -7946,7 +7948,7 @@
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>159</v>
+        <v>310</v>
       </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
@@ -7955,15 +7957,9 @@
       <c r="I121" s="5" t="inlineStr"/>
       <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="5" t="inlineStr"/>
-      <c r="L121" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr"/>
       <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -7985,7 +7981,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7999,7 +7995,7 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr"/>
@@ -8008,9 +8004,15 @@
       <c r="I122" s="5" t="inlineStr"/>
       <c r="J122" s="5" t="inlineStr"/>
       <c r="K122" s="5" t="inlineStr"/>
-      <c r="L122" s="5" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="O122" s="5" t="inlineStr"/>
       <c r="P122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -8219,45 +8221,41 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Warwick Solar Farm 2</t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr"/>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="J126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr"/>
       <c r="L126" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="O126" s="5" t="inlineStr"/>
       <c r="P126" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="Q126" s="5" t="inlineStr"/>
       <c r="R126" s="5" t="n">
@@ -8265,10 +8263,10 @@
       </c>
       <c r="S126" s="5" t="inlineStr"/>
       <c r="T126" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="U126" s="6" t="n">
-        <v>-0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V126" s="5" t="inlineStr"/>
       <c r="W126" s="6" t="inlineStr"/>
@@ -8276,41 +8274,45 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t>Warwick Solar Farm 2</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="5" t="inlineStr"/>
-      <c r="K127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L127" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="O127" s="5" t="inlineStr"/>
       <c r="P127" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="Q127" s="5" t="inlineStr"/>
       <c r="R127" s="5" t="n">
@@ -8318,10 +8320,10 @@
       </c>
       <c r="S127" s="5" t="inlineStr"/>
       <c r="T127" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="U127" s="6" t="n">
-        <v>0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="V127" s="5" t="inlineStr"/>
       <c r="W127" s="6" t="inlineStr"/>
@@ -8329,12 +8331,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Maryrorough Solar Farm</t>
+          <t xml:space="preserve">Warwick Solar Farm 1 </t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -8343,15 +8345,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr"/>
       <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="I128" s="5" t="inlineStr"/>
       <c r="J128" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8388,12 +8388,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Yarranlea Solar Farm</t>
+          <t>Maryrorough Solar Farm</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="5" t="inlineStr"/>
@@ -8447,12 +8447,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warwick Solar Farm 1 </t>
+          <t>Yarranlea Solar Farm</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8461,13 +8461,15 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="J130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8949,62 +8951,72 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>DG_QLD1</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Supernode BESS</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v/>
       </c>
       <c r="D138" s="4" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="5" t="inlineStr"/>
-      <c r="L138" s="5" t="inlineStr"/>
-      <c r="M138" s="5" t="inlineStr"/>
-      <c r="N138" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O138" s="5" t="inlineStr"/>
       <c r="P138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q138" s="5" t="inlineStr"/>
       <c r="R138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S138" s="5" t="inlineStr"/>
       <c r="T138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U138" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="V138" s="5" t="inlineStr"/>
+      <c r="W138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9059,65 +9071,57 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
+          <t>SNB01</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>QLD1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="n"/>
+          <t>Supernode BESS</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D140" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>337.4</v>
+      </c>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
+      <c r="M140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="inlineStr"/>
       <c r="O140" s="5" t="inlineStr"/>
       <c r="P140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" s="5" t="inlineStr"/>
+      <c r="Q140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="R140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S140" s="5" t="inlineStr"/>
+      <c r="S140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="T140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U140" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="5" t="inlineStr"/>
-      <c r="W140" s="6" t="inlineStr"/>
+      <c r="V140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -9903,13 +9907,15 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHL2</t>
+          <t>KIDSPHL1</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
         <v/>
       </c>
-      <c r="C154" s="3" t="n"/>
+      <c r="C154" s="3" t="n">
+        <v/>
+      </c>
       <c r="D154" s="4" t="n">
         <v>160</v>
       </c>
@@ -9938,13 +9944,15 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHL1</t>
+          <t>KIDSPHL2</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
         <v/>
       </c>
-      <c r="C155" s="3" t="n"/>
+      <c r="C155" s="3" t="n">
+        <v/>
+      </c>
       <c r="D155" s="4" t="n">
         <v>160</v>
       </c>
@@ -10048,7 +10056,9 @@
           <t>Suncoast Gold Macadamias</t>
         </is>
       </c>
-      <c r="C157" s="3" t="n"/>
+      <c r="C157" s="3" t="n">
+        <v/>
+      </c>
       <c r="D157" s="4" t="n">
         <v>1</v>
       </c>
@@ -10124,12 +10134,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Whitwood Road Renewable Energy Facility</t>
+          <t>Roghan Road LFG Power Plant</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10138,22 +10148,22 @@
         </is>
       </c>
       <c r="D159" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="J159" s="5" t="inlineStr"/>
       <c r="K159" s="5" t="inlineStr"/>
@@ -10173,12 +10183,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Rochedale Renewable Energy Facility</t>
+          <t>Whitwood Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -10187,22 +10197,22 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="J160" s="5" t="inlineStr"/>
       <c r="K160" s="5" t="inlineStr"/>
@@ -10222,12 +10232,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Roghan Road LFG Power Plant</t>
+          <t>Rochedale Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10236,22 +10246,22 @@
         </is>
       </c>
       <c r="D161" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="J161" s="5" t="inlineStr"/>
       <c r="K161" s="5" t="inlineStr"/>
@@ -10712,7 +10722,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -10752,7 +10762,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -10960,7 +10970,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
@@ -11002,7 +11012,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
@@ -11152,18 +11162,14 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n">
-        <v>1.0107</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0.9715</v>
-      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11238,14 +11244,18 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>1.0107</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.9715</v>
+      </c>
       <c r="E19" s="5" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0.8735000000000001</v>
@@ -11318,7 +11328,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -11344,7 +11354,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
@@ -11490,7 +11500,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>CPP_4</t>
+          <t>CPP_3</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -11536,7 +11546,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>CPP_3</t>
+          <t>CPP_4</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -11656,7 +11666,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -11702,7 +11712,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -11748,7 +11758,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -11786,7 +11796,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -11824,7 +11834,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -11870,7 +11880,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -11916,7 +11926,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-2</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -11962,7 +11972,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>STAN-2</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -12192,7 +12202,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
@@ -12209,20 +12219,16 @@
       <c r="M42" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N42" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P42" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="P42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr"/>
@@ -12239,11 +12245,15 @@
       <c r="M43" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="O43" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="n">
+        <v>0.9247</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12324,7 +12334,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -12416,7 +12426,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -12462,7 +12472,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE2</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -12554,7 +12564,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -12600,7 +12610,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>GSTONE2</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -12646,7 +12656,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
@@ -12674,7 +12684,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
@@ -12910,7 +12920,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>BARRON-1</t>
+          <t>BARRON-2</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -12956,7 +12966,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>BARRON-2</t>
+          <t>BARRON-1</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -13082,7 +13092,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -13174,7 +13184,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -13254,7 +13264,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
@@ -13262,13 +13272,25 @@
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="n">
         <v>0.9574</v>
@@ -13314,7 +13336,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
@@ -13350,7 +13372,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
@@ -13358,25 +13380,13 @@
       <c r="D72" s="5" t="inlineStr"/>
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
       <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="M72" s="5" t="inlineStr"/>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="n">
         <v>0.9574</v>
@@ -13412,7 +13422,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -13458,7 +13468,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -13504,7 +13514,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -13596,7 +13606,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -13714,7 +13724,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
@@ -13725,15 +13735,9 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="n">
-        <v>0.9586</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>0.9762</v>
-      </c>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr"/>
       <c r="M81" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -13750,7 +13754,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
@@ -13761,9 +13765,15 @@
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="5" t="inlineStr"/>
-      <c r="L82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0.9762</v>
+      </c>
       <c r="M82" s="5" t="n">
         <v>0.962</v>
       </c>
@@ -14056,7 +14066,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
@@ -14102,7 +14112,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
@@ -14194,7 +14204,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -14348,7 +14358,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -14394,7 +14404,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#1</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -14440,7 +14450,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -14486,7 +14496,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>TARONG#1</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -14888,7 +14898,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MPP_1</t>
+          <t>MPP_2</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -14934,7 +14944,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MPP_2</t>
+          <t>MPP_1</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -15054,38 +15064,28 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>GROSV2</t>
+          <t>EDENVSF1</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr"/>
-      <c r="D113" s="5" t="n">
-        <v>1.0252</v>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0.9683</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0.9567</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0.9844000000000001</v>
-      </c>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.9821</v>
+        <v>0.972</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9707</v>
       </c>
       <c r="L113" s="5" t="inlineStr"/>
       <c r="M113" s="5" t="n">
-        <v>0.9977</v>
+        <v>0.9823</v>
       </c>
       <c r="N113" s="5" t="inlineStr"/>
       <c r="O113" s="5" t="n">
@@ -15096,13 +15096,11 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>GROSV1</t>
+          <t>GROSV2</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr"/>
-      <c r="C114" s="5" t="n">
-        <v>1.0727</v>
-      </c>
+      <c r="C114" s="5" t="inlineStr"/>
       <c r="D114" s="5" t="n">
         <v>1.0252</v>
       </c>
@@ -15140,28 +15138,40 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>EDENVSF1</t>
+          <t>GROSV1</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr"/>
-      <c r="C115" s="5" t="inlineStr"/>
-      <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr"/>
-      <c r="H115" s="5" t="inlineStr"/>
+      <c r="C115" s="5" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>1.0252</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0.9683</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.9844000000000001</v>
+      </c>
       <c r="I115" s="5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0.972</v>
+        <v>0.9821</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>0.9707</v>
+        <v>0.9907</v>
       </c>
       <c r="L115" s="5" t="inlineStr"/>
       <c r="M115" s="5" t="n">
-        <v>0.9823</v>
+        <v>0.9977</v>
       </c>
       <c r="N115" s="5" t="inlineStr"/>
       <c r="O115" s="5" t="n">
@@ -15350,7 +15360,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WANDSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr"/>
@@ -15360,15 +15370,9 @@
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="J121" s="5" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0.9785</v>
-      </c>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr"/>
+      <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15382,7 +15386,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>WANDSF2</t>
+          <t>WANDSF1</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr"/>
@@ -15392,9 +15396,15 @@
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="5" t="inlineStr"/>
-      <c r="K122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>0.9785</v>
+      </c>
       <c r="L122" s="5" t="inlineStr"/>
       <c r="M122" s="5" t="n">
         <v>0.9975000000000001</v>
@@ -15532,7 +15542,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr"/>
@@ -15540,24 +15550,20 @@
       <c r="D126" s="5" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="5" t="n">
@@ -15568,7 +15574,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr"/>
@@ -15576,20 +15582,24 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="I127" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="N127" s="5" t="inlineStr"/>
       <c r="O127" s="5" t="n">
@@ -15600,16 +15610,14 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr"/>
       <c r="C128" s="5" t="inlineStr"/>
       <c r="D128" s="5" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -15638,7 +15646,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr"/>
@@ -15676,14 +15684,16 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr"/>
       <c r="C130" s="5" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
+      <c r="F130" s="5" t="n">
+        <v>0.9872</v>
+      </c>
       <c r="G130" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -16002,37 +16012,53 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr"/>
-      <c r="C138" s="5" t="inlineStr"/>
-      <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="5" t="inlineStr"/>
+          <t>DG_QLD1</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N138" s="5" t="inlineStr"/>
       <c r="O138" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P138" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr"/>
@@ -16062,48 +16088,32 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>SNB01</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr"/>
+      <c r="C140" s="5" t="inlineStr"/>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr"/>
       <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P140" s="5" t="inlineStr"/>
+      <c r="P140" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -16616,7 +16626,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHL2</t>
+          <t>KIDSPHL1</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr"/>
@@ -16640,7 +16650,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHL1</t>
+          <t>KIDSPHL2</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr"/>
@@ -16764,23 +16774,23 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="G159" s="5" t="inlineStr"/>
       <c r="H159" s="5" t="inlineStr"/>
@@ -16796,23 +16806,23 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="G160" s="5" t="inlineStr"/>
       <c r="H160" s="5" t="inlineStr"/>
@@ -16828,23 +16838,23 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="G161" s="5" t="inlineStr"/>
       <c r="H161" s="5" t="inlineStr"/>
@@ -17239,7 +17249,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -17268,7 +17278,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -17384,12 +17394,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -17413,12 +17423,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -17529,12 +17539,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17558,12 +17568,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -17645,12 +17655,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17703,12 +17713,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -17805,7 +17815,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -17863,7 +17873,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -18124,7 +18134,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -18153,7 +18163,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -18211,12 +18221,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -18240,12 +18250,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -18356,12 +18366,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Darling Downs Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
